--- a/docs/product-design/migration-copilot/06-fixtures/realistic-exports/karbon-all-contacts.xlsx
+++ b/docs/product-design/migration-copilot/06-fixtures/realistic-exports/karbon-all-contacts.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="215">
   <si>
     <t>ContactKey</t>
   </si>
@@ -76,7 +76,7 @@
     <t>CA</t>
   </si>
   <si>
-    <t>1065; In Progress</t>
+    <t>1065; Ready for Review</t>
   </si>
   <si>
     <t>In Progress</t>
@@ -106,7 +106,7 @@
     <t>NY</t>
   </si>
   <si>
-    <t>1065; Waiting on client</t>
+    <t>1065; On Extension</t>
   </si>
   <si>
     <t>Waiting on client</t>
@@ -136,7 +136,7 @@
     <t>TX</t>
   </si>
   <si>
-    <t>1120; Ready for review</t>
+    <t>1120; Waiting on Client</t>
   </si>
   <si>
     <t>Ready for review</t>
@@ -169,7 +169,7 @@
     <t>FL</t>
   </si>
   <si>
-    <t>1040; Organizer sent</t>
+    <t>1040; Complete</t>
   </si>
   <si>
     <t>Organizer sent</t>
@@ -196,7 +196,7 @@
     <t>WA</t>
   </si>
   <si>
-    <t>1065; Open items</t>
+    <t>1065; Not Started</t>
   </si>
   <si>
     <t>Open items</t>
@@ -223,7 +223,7 @@
     <t>IL</t>
   </si>
   <si>
-    <t>1041; Extension filed</t>
+    <t>1041; In Progress</t>
   </si>
   <si>
     <t>Extension filed</t>
@@ -247,7 +247,7 @@
     <t>99-1000007</t>
   </si>
   <si>
-    <t>Schedule C; Needs bookkeeping</t>
+    <t>Schedule C; Ready for Review</t>
   </si>
   <si>
     <t>Needs bookkeeping</t>
@@ -271,7 +271,7 @@
     <t>99-1000008</t>
   </si>
   <si>
-    <t>990; Board review</t>
+    <t>990; On Extension</t>
   </si>
   <si>
     <t>Board review</t>
@@ -295,7 +295,7 @@
     <t>99-1000009</t>
   </si>
   <si>
-    <t>1065; In progress</t>
+    <t>1065; Waiting on Client</t>
   </si>
   <si>
     <t>In progress</t>
@@ -319,7 +319,7 @@
     <t>99-1000010</t>
   </si>
   <si>
-    <t>1120S; Ready for e-file</t>
+    <t>1120S; Complete</t>
   </si>
   <si>
     <t>Ready for e-file</t>
@@ -343,7 +343,7 @@
     <t>99-1000011</t>
   </si>
   <si>
-    <t>1120; R&amp;D credit review</t>
+    <t>1120; Not Started</t>
   </si>
   <si>
     <t>R&amp;D credit review</t>
@@ -367,7 +367,7 @@
     <t>99-1000012</t>
   </si>
   <si>
-    <t>1040; Missing K-1</t>
+    <t>1040; In Progress</t>
   </si>
   <si>
     <t>Missing K-1</t>
@@ -391,9 +391,6 @@
     <t>99-1000013</t>
   </si>
   <si>
-    <t>1065; Partner capital review</t>
-  </si>
-  <si>
     <t>Partner capital review</t>
   </si>
   <si>
@@ -415,7 +412,7 @@
     <t>99-1000014</t>
   </si>
   <si>
-    <t>1041; Beneficiary update</t>
+    <t>1041; On Extension</t>
   </si>
   <si>
     <t>Beneficiary update</t>
@@ -439,7 +436,7 @@
     <t>99-1000015</t>
   </si>
   <si>
-    <t>Schedule C; Mileage log pending</t>
+    <t>Schedule C; Waiting on Client</t>
   </si>
   <si>
     <t>Mileage log pending</t>
@@ -463,7 +460,7 @@
     <t>99-1000016</t>
   </si>
   <si>
-    <t>1065; Multi-member LLC</t>
+    <t>1065; Complete</t>
   </si>
   <si>
     <t>Multi-member LLC</t>
@@ -487,7 +484,7 @@
     <t>99-1000017</t>
   </si>
   <si>
-    <t>1120S; Payroll tie-out</t>
+    <t>1120S; Not Started</t>
   </si>
   <si>
     <t>Payroll tie-out</t>
@@ -511,7 +508,7 @@
     <t>99-1000018</t>
   </si>
   <si>
-    <t>1120; Inventory review</t>
+    <t>1120; In Progress</t>
   </si>
   <si>
     <t>Inventory review</t>
@@ -538,9 +535,6 @@
     <t/>
   </si>
   <si>
-    <t>1065; Review: missing filing state</t>
-  </si>
-  <si>
     <t>Review: missing filing state</t>
   </si>
   <si>
@@ -565,7 +559,7 @@
     <t>C.A.</t>
   </si>
   <si>
-    <t>1120S; Review: state exported as C.A.</t>
+    <t>1120S; On Extension</t>
   </si>
   <si>
     <t>Review: state exported as C.A.</t>
@@ -589,9 +583,6 @@
     <t>99-1000021</t>
   </si>
   <si>
-    <t>1065; Owner basis review</t>
-  </si>
-  <si>
     <t>Owner basis review</t>
   </si>
   <si>
@@ -613,9 +604,6 @@
     <t>99-1000022</t>
   </si>
   <si>
-    <t>1040; Schedule E rental</t>
-  </si>
-  <si>
     <t>Schedule E rental</t>
   </si>
   <si>
@@ -637,7 +625,7 @@
     <t>99-1000023</t>
   </si>
   <si>
-    <t>1041; Estimated tax review</t>
+    <t>1041; Not Started</t>
   </si>
   <si>
     <t>Estimated tax review</t>
@@ -661,7 +649,7 @@
     <t>99-1000024</t>
   </si>
   <si>
-    <t>990; Grant schedule review</t>
+    <t>990; In Progress</t>
   </si>
   <si>
     <t>Grant schedule review</t>
@@ -1199,27 +1187,27 @@
         <v>21</v>
       </c>
       <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
         <v>127</v>
-      </c>
-      <c r="L14" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" t="s">
         <v>129</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>130</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>131</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>132</v>
-      </c>
-      <c r="E15" t="s">
-        <v>133</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -1228,7 +1216,7 @@
         <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
@@ -1237,27 +1225,27 @@
         <v>31</v>
       </c>
       <c r="K15" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" t="s">
         <v>135</v>
-      </c>
-      <c r="L15" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" t="s">
         <v>137</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>138</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>139</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>140</v>
-      </c>
-      <c r="E16" t="s">
-        <v>141</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
@@ -1266,7 +1254,7 @@
         <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
@@ -1275,27 +1263,27 @@
         <v>41</v>
       </c>
       <c r="K16" t="s">
+        <v>142</v>
+      </c>
+      <c r="L16" t="s">
         <v>143</v>
-      </c>
-      <c r="L16" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" t="s">
         <v>145</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>146</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>147</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>148</v>
-      </c>
-      <c r="E17" t="s">
-        <v>149</v>
       </c>
       <c r="F17" t="s">
         <v>49</v>
@@ -1304,7 +1292,7 @@
         <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I17" t="s">
         <v>20</v>
@@ -1313,27 +1301,27 @@
         <v>52</v>
       </c>
       <c r="K17" t="s">
+        <v>150</v>
+      </c>
+      <c r="L17" t="s">
         <v>151</v>
-      </c>
-      <c r="L17" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" t="s">
         <v>153</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>154</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>155</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>156</v>
-      </c>
-      <c r="E18" t="s">
-        <v>157</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
@@ -1342,7 +1330,7 @@
         <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I18" t="s">
         <v>20</v>
@@ -1351,27 +1339,27 @@
         <v>61</v>
       </c>
       <c r="K18" t="s">
+        <v>158</v>
+      </c>
+      <c r="L18" t="s">
         <v>159</v>
-      </c>
-      <c r="L18" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" t="s">
         <v>161</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>162</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>163</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>164</v>
-      </c>
-      <c r="E19" t="s">
-        <v>165</v>
       </c>
       <c r="F19" t="s">
         <v>29</v>
@@ -1380,7 +1368,7 @@
         <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I19" t="s">
         <v>20</v>
@@ -1389,27 +1377,27 @@
         <v>70</v>
       </c>
       <c r="K19" t="s">
+        <v>166</v>
+      </c>
+      <c r="L19" t="s">
         <v>167</v>
-      </c>
-      <c r="L19" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" t="s">
         <v>169</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>170</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>171</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>172</v>
-      </c>
-      <c r="E20" t="s">
-        <v>173</v>
       </c>
       <c r="F20" t="s">
         <v>39</v>
@@ -1418,36 +1406,36 @@
         <v>18</v>
       </c>
       <c r="H20" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s">
         <v>174</v>
       </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
         <v>175</v>
-      </c>
-      <c r="K20" t="s">
-        <v>176</v>
-      </c>
-      <c r="L20" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" t="s">
         <v>178</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>179</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>180</v>
-      </c>
-      <c r="D21" t="s">
-        <v>181</v>
-      </c>
-      <c r="E21" t="s">
-        <v>182</v>
       </c>
       <c r="F21" t="s">
         <v>49</v>
@@ -1456,36 +1444,36 @@
         <v>18</v>
       </c>
       <c r="H21" t="s">
+        <v>181</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" t="s">
+        <v>182</v>
+      </c>
+      <c r="K21" t="s">
         <v>183</v>
       </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="L21" t="s">
         <v>184</v>
-      </c>
-      <c r="K21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L21" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>185</v>
+      </c>
+      <c r="B22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" t="s">
         <v>187</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>188</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>189</v>
-      </c>
-      <c r="D22" t="s">
-        <v>190</v>
-      </c>
-      <c r="E22" t="s">
-        <v>191</v>
       </c>
       <c r="F22" t="s">
         <v>17</v>
@@ -1494,7 +1482,7 @@
         <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -1503,27 +1491,27 @@
         <v>31</v>
       </c>
       <c r="K22" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="L22" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" t="s">
         <v>195</v>
       </c>
-      <c r="B23" t="s">
+      <c r="E23" t="s">
         <v>196</v>
-      </c>
-      <c r="C23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D23" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" t="s">
-        <v>199</v>
       </c>
       <c r="F23" t="s">
         <v>29</v>
@@ -1532,7 +1520,7 @@
         <v>50</v>
       </c>
       <c r="H23" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I23" t="s">
         <v>20</v>
@@ -1541,27 +1529,27 @@
         <v>41</v>
       </c>
       <c r="K23" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="L23" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>199</v>
+      </c>
+      <c r="B24" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" t="s">
+        <v>201</v>
+      </c>
+      <c r="D24" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" t="s">
         <v>203</v>
-      </c>
-      <c r="B24" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" t="s">
-        <v>205</v>
-      </c>
-      <c r="D24" t="s">
-        <v>206</v>
-      </c>
-      <c r="E24" t="s">
-        <v>207</v>
       </c>
       <c r="F24" t="s">
         <v>39</v>
@@ -1570,7 +1558,7 @@
         <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I24" t="s">
         <v>20</v>
@@ -1579,27 +1567,27 @@
         <v>52</v>
       </c>
       <c r="K24" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L24" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D25" t="s">
+        <v>210</v>
+      </c>
+      <c r="E25" t="s">
         <v>211</v>
-      </c>
-      <c r="B25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C25" t="s">
-        <v>213</v>
-      </c>
-      <c r="D25" t="s">
-        <v>214</v>
-      </c>
-      <c r="E25" t="s">
-        <v>215</v>
       </c>
       <c r="F25" t="s">
         <v>49</v>
@@ -1608,7 +1596,7 @@
         <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I25" t="s">
         <v>20</v>
@@ -1617,10 +1605,10 @@
         <v>61</v>
       </c>
       <c r="K25" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L25" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/docs/product-design/migration-copilot/06-fixtures/realistic-exports/karbon-all-contacts.xlsx
+++ b/docs/product-design/migration-copilot/06-fixtures/realistic-exports/karbon-all-contacts.xlsx
@@ -8,658 +8,838 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="215">
-  <si>
-    <t>ContactKey</t>
-  </si>
-  <si>
-    <t>OrganizationKey</t>
-  </si>
-  <si>
-    <t>Organization Name</t>
-  </si>
-  <si>
-    <t>Contact Name</t>
-  </si>
-  <si>
-    <t>Contact Email</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="275">
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Contact Type</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Entity Type</t>
   </si>
   <si>
     <t>Client Owner</t>
   </si>
   <si>
-    <t>Contact Type</t>
-  </si>
-  <si>
-    <t>Tax ID</t>
+    <t>Client Manager</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
   </si>
   <si>
     <t>Country</t>
   </si>
   <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Tags</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>KCON-3001</t>
-  </si>
-  <si>
-    <t>KORG-5001</t>
-  </si>
-  <si>
-    <t>Marin Harbor Analytics LLC (TEST)</t>
+    <t>9GqDTmnopqrs</t>
+  </si>
+  <si>
+    <t>Client</t>
   </si>
   <si>
     <t>Jordan Park</t>
   </si>
   <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Park</t>
+  </si>
+  <si>
+    <t>LLC</t>
+  </si>
+  <si>
+    <t>J. Doe</t>
+  </si>
+  <si>
+    <t>Dana Lee</t>
+  </si>
+  <si>
     <t>test+realistic001@example.com</t>
   </si>
   <si>
-    <t>M-LEE</t>
-  </si>
-  <si>
-    <t>Organization</t>
-  </si>
-  <si>
-    <t>99-1000001</t>
+    <t>555-0101</t>
+  </si>
+  <si>
+    <t>1001 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>90012</t>
   </si>
   <si>
     <t>United States</t>
   </si>
   <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>1065; Ready for Review</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>KCON-3002</t>
-  </si>
-  <si>
-    <t>KORG-5002</t>
-  </si>
-  <si>
-    <t>Hudson Ledger Partners LP (TEST)</t>
+    <t>8cF3yuuvwxyz</t>
   </si>
   <si>
     <t>Riley Chen</t>
   </si>
   <si>
+    <t>Riley</t>
+  </si>
+  <si>
+    <t>Chen</t>
+  </si>
+  <si>
+    <t>Partnership</t>
+  </si>
+  <si>
+    <t>R. Chen</t>
+  </si>
+  <si>
+    <t>Avery Park</t>
+  </si>
+  <si>
     <t>test+realistic002@example.com</t>
   </si>
   <si>
-    <t>M-PARK</t>
-  </si>
-  <si>
-    <t>99-1000002</t>
+    <t>555-0102</t>
+  </si>
+  <si>
+    <t>1002 Ledger Lane</t>
+  </si>
+  <si>
+    <t>New York</t>
   </si>
   <si>
     <t>NY</t>
   </si>
   <si>
-    <t>1065; On Extension</t>
-  </si>
-  <si>
-    <t>Waiting on client</t>
-  </si>
-  <si>
-    <t>KCON-3003</t>
-  </si>
-  <si>
-    <t>KORG-5003</t>
-  </si>
-  <si>
-    <t>Austin Foundry Inc (TEST)</t>
+    <t>10018</t>
+  </si>
+  <si>
+    <t>7ITteCBCDEFG</t>
   </si>
   <si>
     <t>Morgan Lee</t>
   </si>
   <si>
+    <t>Morgan</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>C-Corp</t>
+  </si>
+  <si>
+    <t>M. Lee</t>
+  </si>
+  <si>
+    <t>Robin Rivera</t>
+  </si>
+  <si>
     <t>test+realistic003@example.com</t>
   </si>
   <si>
-    <t>M-RIVERA</t>
-  </si>
-  <si>
-    <t>99-1000003</t>
+    <t>555-0103</t>
+  </si>
+  <si>
+    <t>1003 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Austin</t>
   </si>
   <si>
     <t>TX</t>
   </si>
   <si>
-    <t>1120; Waiting on Client</t>
-  </si>
-  <si>
-    <t>Ready for review</t>
-  </si>
-  <si>
-    <t>KCON-3004</t>
-  </si>
-  <si>
-    <t>KORG-5004</t>
-  </si>
-  <si>
-    <t>Bayview Stone Household (TEST)</t>
+    <t>78701</t>
+  </si>
+  <si>
+    <t>6e8TTJIJKLMN</t>
   </si>
   <si>
     <t>Taylor Kim</t>
   </si>
   <si>
+    <t>Taylor</t>
+  </si>
+  <si>
+    <t>Kim</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>T. Kim</t>
+  </si>
+  <si>
+    <t>Sky Stone</t>
+  </si>
+  <si>
     <t>test+realistic004@example.com</t>
   </si>
   <si>
-    <t>M-STONE</t>
-  </si>
-  <si>
-    <t>Person</t>
-  </si>
-  <si>
-    <t>99-1000004</t>
+    <t>555-0104</t>
+  </si>
+  <si>
+    <t>1004 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Miami</t>
   </si>
   <si>
     <t>FL</t>
   </si>
   <si>
-    <t>1040; Complete</t>
-  </si>
-  <si>
-    <t>Organizer sent</t>
-  </si>
-  <si>
-    <t>KCON-3005</t>
-  </si>
-  <si>
-    <t>KORG-5005</t>
-  </si>
-  <si>
-    <t>Cascade Orchard LLC (TEST)</t>
+    <t>33131</t>
+  </si>
+  <si>
+    <t>39JZdPPQRSTU</t>
   </si>
   <si>
     <t>Parker Vu</t>
   </si>
   <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>Vu</t>
+  </si>
+  <si>
+    <t>P. Vu</t>
+  </si>
+  <si>
     <t>test+realistic005@example.com</t>
   </si>
   <si>
-    <t>99-1000005</t>
+    <t>555-0105</t>
+  </si>
+  <si>
+    <t>1005 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Seattle</t>
   </si>
   <si>
     <t>WA</t>
   </si>
   <si>
-    <t>1065; Not Started</t>
-  </si>
-  <si>
-    <t>Open items</t>
-  </si>
-  <si>
-    <t>KCON-3006</t>
-  </si>
-  <si>
-    <t>KORG-5006</t>
-  </si>
-  <si>
-    <t>Prairie Oak Trust (TEST)</t>
+    <t>98101</t>
+  </si>
+  <si>
+    <t>2FYpTWWXYZ01</t>
   </si>
   <si>
     <t>Sam Rivera</t>
   </si>
   <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>Rivera</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>S. Rivera</t>
+  </si>
+  <si>
     <t>test+realistic006@example.com</t>
   </si>
   <si>
-    <t>99-1000006</t>
+    <t>555-0106</t>
+  </si>
+  <si>
+    <t>1006 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Chicago</t>
   </si>
   <si>
     <t>IL</t>
   </si>
   <si>
-    <t>1041; In Progress</t>
-  </si>
-  <si>
-    <t>Extension filed</t>
-  </si>
-  <si>
-    <t>KCON-3007</t>
-  </si>
-  <si>
-    <t>KORG-5007</t>
-  </si>
-  <si>
-    <t>Golden Gate Studio (TEST)</t>
+    <t>60603</t>
+  </si>
+  <si>
+    <t>1bdQy4345678</t>
   </si>
   <si>
     <t>Alex Nguyen</t>
   </si>
   <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Nguyen</t>
+  </si>
+  <si>
+    <t>A. Nguyen</t>
+  </si>
+  <si>
     <t>test+realistic007@example.com</t>
   </si>
   <si>
-    <t>99-1000007</t>
-  </si>
-  <si>
-    <t>Schedule C; Ready for Review</t>
-  </si>
-  <si>
-    <t>Needs bookkeeping</t>
-  </si>
-  <si>
-    <t>KCON-3008</t>
-  </si>
-  <si>
-    <t>KORG-5008</t>
-  </si>
-  <si>
-    <t>Brooklyn Outreach Foundation (TEST)</t>
+    <t>555-0107</t>
+  </si>
+  <si>
+    <t>1007 Ledger Lane</t>
+  </si>
+  <si>
+    <t>San Francisco</t>
+  </si>
+  <si>
+    <t>94105</t>
+  </si>
+  <si>
+    <t>0Hrgecbcdefg</t>
   </si>
   <si>
     <t>Casey Brooks</t>
   </si>
   <si>
+    <t>Casey</t>
+  </si>
+  <si>
+    <t>Brooks</t>
+  </si>
+  <si>
+    <t>Nonprofit</t>
+  </si>
+  <si>
+    <t>C. Brooks</t>
+  </si>
+  <si>
     <t>test+realistic008@example.com</t>
   </si>
   <si>
-    <t>99-1000008</t>
-  </si>
-  <si>
-    <t>990; On Extension</t>
-  </si>
-  <si>
-    <t>Board review</t>
-  </si>
-  <si>
-    <t>KCON-3009</t>
-  </si>
-  <si>
-    <t>KORG-5009</t>
-  </si>
-  <si>
-    <t>Hill Country Advisors LLC (TEST)</t>
+    <t>555-0108</t>
+  </si>
+  <si>
+    <t>1008 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Brooklyn</t>
+  </si>
+  <si>
+    <t>11201</t>
+  </si>
+  <si>
+    <t>XC3lyhijklmn</t>
   </si>
   <si>
     <t>Jamie Patel</t>
   </si>
   <si>
+    <t>Jamie</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>J. Patel</t>
+  </si>
+  <si>
     <t>test+realistic009@example.com</t>
   </si>
   <si>
-    <t>99-1000009</t>
-  </si>
-  <si>
-    <t>1065; Waiting on Client</t>
-  </si>
-  <si>
-    <t>In progress</t>
-  </si>
-  <si>
-    <t>KCON-3010</t>
-  </si>
-  <si>
-    <t>KORG-5010</t>
-  </si>
-  <si>
-    <t>Palm River Dental PC (TEST)</t>
+    <t>555-0109</t>
+  </si>
+  <si>
+    <t>1009 Ledger Lane</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>78205</t>
+  </si>
+  <si>
+    <t>W8hMdppqrstu</t>
   </si>
   <si>
     <t>Avery Stone</t>
   </si>
   <si>
+    <t>Avery</t>
+  </si>
+  <si>
+    <t>Stone</t>
+  </si>
+  <si>
+    <t>S-Corp</t>
+  </si>
+  <si>
+    <t>A. Stone</t>
+  </si>
+  <si>
     <t>test+realistic010@example.com</t>
   </si>
   <si>
-    <t>99-1000010</t>
-  </si>
-  <si>
-    <t>1120S; Complete</t>
-  </si>
-  <si>
-    <t>Ready for e-file</t>
-  </si>
-  <si>
-    <t>KCON-3011</t>
-  </si>
-  <si>
-    <t>KORG-5011</t>
-  </si>
-  <si>
-    <t>Puget Sound Robotics Inc (TEST)</t>
+    <t>555-0110</t>
+  </si>
+  <si>
+    <t>1010 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Tampa</t>
+  </si>
+  <si>
+    <t>33602</t>
+  </si>
+  <si>
+    <t>VEwcTwwxyzAB</t>
   </si>
   <si>
     <t>Drew Morris</t>
   </si>
   <si>
+    <t>Drew</t>
+  </si>
+  <si>
+    <t>Morris</t>
+  </si>
+  <si>
+    <t>D. Morris</t>
+  </si>
+  <si>
     <t>test+realistic011@example.com</t>
   </si>
   <si>
-    <t>99-1000011</t>
-  </si>
-  <si>
-    <t>1120; Not Started</t>
-  </si>
-  <si>
-    <t>R&amp;D credit review</t>
-  </si>
-  <si>
-    <t>KCON-3012</t>
-  </si>
-  <si>
-    <t>KORG-5012</t>
-  </si>
-  <si>
-    <t>Lincoln Park Household (TEST)</t>
+    <t>555-0111</t>
+  </si>
+  <si>
+    <t>1011 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Bellevue</t>
+  </si>
+  <si>
+    <t>98004</t>
+  </si>
+  <si>
+    <t>UaLCyEDEFGHI</t>
   </si>
   <si>
     <t>Quinn Reed</t>
   </si>
   <si>
+    <t>Quinn</t>
+  </si>
+  <si>
+    <t>Reed</t>
+  </si>
+  <si>
+    <t>Q. Reed</t>
+  </si>
+  <si>
     <t>test+realistic012@example.com</t>
   </si>
   <si>
-    <t>99-1000012</t>
-  </si>
-  <si>
-    <t>1040; In Progress</t>
-  </si>
-  <si>
-    <t>Missing K-1</t>
-  </si>
-  <si>
-    <t>KCON-3013</t>
-  </si>
-  <si>
-    <t>KORG-5013</t>
-  </si>
-  <si>
-    <t>Silicon Coast Ventures LP (TEST)</t>
+    <t>555-0112</t>
+  </si>
+  <si>
+    <t>1012 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Evanston</t>
+  </si>
+  <si>
+    <t>60201</t>
+  </si>
+  <si>
+    <t>R5mISJKLMNOP</t>
   </si>
   <si>
     <t>Hayden Flores</t>
   </si>
   <si>
+    <t>Hayden</t>
+  </si>
+  <si>
+    <t>Flores</t>
+  </si>
+  <si>
+    <t>H. Flores</t>
+  </si>
+  <si>
     <t>test+realistic013@example.com</t>
   </si>
   <si>
-    <t>99-1000013</t>
-  </si>
-  <si>
-    <t>Partner capital review</t>
-  </si>
-  <si>
-    <t>KCON-3014</t>
-  </si>
-  <si>
-    <t>KORG-5014</t>
-  </si>
-  <si>
-    <t>Rochester Maple Trust (TEST)</t>
+    <t>555-0113</t>
+  </si>
+  <si>
+    <t>1013 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Palo Alto</t>
+  </si>
+  <si>
+    <t>94301</t>
+  </si>
+  <si>
+    <t>QBB8xRRSTUVW</t>
   </si>
   <si>
     <t>Rowan Foster</t>
   </si>
   <si>
+    <t>Rowan</t>
+  </si>
+  <si>
+    <t>Foster</t>
+  </si>
+  <si>
+    <t>R. Foster</t>
+  </si>
+  <si>
     <t>test+realistic014@example.com</t>
   </si>
   <si>
-    <t>99-1000014</t>
-  </si>
-  <si>
-    <t>1041; On Extension</t>
-  </si>
-  <si>
-    <t>Beneficiary update</t>
-  </si>
-  <si>
-    <t>KCON-3015</t>
-  </si>
-  <si>
-    <t>KORG-5015</t>
-  </si>
-  <si>
-    <t>Dallas Market Studio (TEST)</t>
+    <t>555-0114</t>
+  </si>
+  <si>
+    <t>1014 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Rochester</t>
+  </si>
+  <si>
+    <t>14604</t>
+  </si>
+  <si>
+    <t>P7PydZYZ0123</t>
   </si>
   <si>
     <t>Emerson Gray</t>
   </si>
   <si>
+    <t>Emerson</t>
+  </si>
+  <si>
+    <t>Gray</t>
+  </si>
+  <si>
+    <t>E. Gray</t>
+  </si>
+  <si>
     <t>test+realistic015@example.com</t>
   </si>
   <si>
-    <t>99-1000015</t>
-  </si>
-  <si>
-    <t>Schedule C; Waiting on Client</t>
-  </si>
-  <si>
-    <t>Mileage log pending</t>
-  </si>
-  <si>
-    <t>KCON-3016</t>
-  </si>
-  <si>
-    <t>KORG-5016</t>
-  </si>
-  <si>
-    <t>Orlando Harbor LLC (TEST)</t>
+    <t>555-0115</t>
+  </si>
+  <si>
+    <t>1015 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>75201</t>
+  </si>
+  <si>
+    <t>OD4YS656789a</t>
   </si>
   <si>
     <t>Harper Miles</t>
   </si>
   <si>
+    <t>Harper</t>
+  </si>
+  <si>
+    <t>Miles</t>
+  </si>
+  <si>
+    <t>H. Miles</t>
+  </si>
+  <si>
     <t>test+realistic016@example.com</t>
   </si>
   <si>
-    <t>99-1000016</t>
-  </si>
-  <si>
-    <t>1065; Complete</t>
-  </si>
-  <si>
-    <t>Multi-member LLC</t>
-  </si>
-  <si>
-    <t>KCON-3017</t>
-  </si>
-  <si>
-    <t>KORG-5017</t>
-  </si>
-  <si>
-    <t>Spokane Design Group Inc (TEST)</t>
+    <t>555-0116</t>
+  </si>
+  <si>
+    <t>1016 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>32801</t>
+  </si>
+  <si>
+    <t>LyG4ccdefghi</t>
   </si>
   <si>
     <t>Finley Cooper</t>
   </si>
   <si>
+    <t>Finley</t>
+  </si>
+  <si>
+    <t>Cooper</t>
+  </si>
+  <si>
+    <t>F. Cooper</t>
+  </si>
+  <si>
     <t>test+realistic017@example.com</t>
   </si>
   <si>
-    <t>99-1000017</t>
-  </si>
-  <si>
-    <t>1120S; Not Started</t>
-  </si>
-  <si>
-    <t>Payroll tie-out</t>
-  </si>
-  <si>
-    <t>KCON-3018</t>
-  </si>
-  <si>
-    <t>KORG-5018</t>
-  </si>
-  <si>
-    <t>River North Supply Inc (TEST)</t>
+    <t>555-0117</t>
+  </si>
+  <si>
+    <t>1017 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Spokane</t>
+  </si>
+  <si>
+    <t>99201</t>
+  </si>
+  <si>
+    <t>K4UuSjklmnop</t>
   </si>
   <si>
     <t>Reese Bennett</t>
   </si>
   <si>
+    <t>Reese</t>
+  </si>
+  <si>
+    <t>Bennett</t>
+  </si>
+  <si>
+    <t>R. Bennett</t>
+  </si>
+  <si>
     <t>test+realistic018@example.com</t>
   </si>
   <si>
-    <t>99-1000018</t>
-  </si>
-  <si>
-    <t>1120; In Progress</t>
-  </si>
-  <si>
-    <t>Inventory review</t>
-  </si>
-  <si>
-    <t>KCON-3019</t>
-  </si>
-  <si>
-    <t>KORG-5019</t>
-  </si>
-  <si>
-    <t>North Star Clinic LLC (TEST)</t>
+    <t>555-0118</t>
+  </si>
+  <si>
+    <t>1018 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Naperville</t>
+  </si>
+  <si>
+    <t>60540</t>
+  </si>
+  <si>
+    <t>JA9Uxrrstuvw</t>
   </si>
   <si>
     <t>Sloane Carter</t>
   </si>
   <si>
+    <t>Sloane</t>
+  </si>
+  <si>
+    <t>Carter</t>
+  </si>
+  <si>
+    <t>S. Carter</t>
+  </si>
+  <si>
     <t>test+realistic019@example.com</t>
   </si>
   <si>
-    <t>99-1000019</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Review: missing filing state</t>
-  </si>
-  <si>
-    <t>KCON-3020</t>
-  </si>
-  <si>
-    <t>KORG-5020</t>
-  </si>
-  <si>
-    <t>Pacific Crest Therapy Inc (TEST)</t>
+    <t>555-0119</t>
+  </si>
+  <si>
+    <t>1019 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>80202</t>
+  </si>
+  <si>
+    <t>I6nldzyzABCD</t>
   </si>
   <si>
     <t>Dakota Price</t>
   </si>
   <si>
+    <t>Dakota</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>D. Price</t>
+  </si>
+  <si>
     <t>test+realistic020@example.com</t>
   </si>
   <si>
-    <t>99-1000020</t>
-  </si>
-  <si>
-    <t>C.A.</t>
-  </si>
-  <si>
-    <t>1120S; On Extension</t>
-  </si>
-  <si>
-    <t>Review: state exported as C.A.</t>
-  </si>
-  <si>
-    <t>KCON-3021</t>
-  </si>
-  <si>
-    <t>KORG-5021</t>
-  </si>
-  <si>
-    <t>Queensboro Catering LP (TEST)</t>
+    <t>555-0120</t>
+  </si>
+  <si>
+    <t>1020 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Irvine</t>
+  </si>
+  <si>
+    <t>92614</t>
+  </si>
+  <si>
+    <t>HCCLSGFGHIJK</t>
   </si>
   <si>
     <t>Skyler Ward</t>
   </si>
   <si>
+    <t>Skyler</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
+    <t>S. Ward</t>
+  </si>
+  <si>
     <t>test+realistic021@example.com</t>
   </si>
   <si>
-    <t>99-1000021</t>
-  </si>
-  <si>
-    <t>Owner basis review</t>
-  </si>
-  <si>
-    <t>KCON-3022</t>
-  </si>
-  <si>
-    <t>KORG-5022</t>
-  </si>
-  <si>
-    <t>Fort Worth Household (TEST)</t>
+    <t>555-0121</t>
+  </si>
+  <si>
+    <t>1021 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Queens</t>
+  </si>
+  <si>
+    <t>11101</t>
+  </si>
+  <si>
+    <t>ExeRcMMNOPQR</t>
   </si>
   <si>
     <t>Blake Young</t>
   </si>
   <si>
+    <t>Blake</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>B. Young</t>
+  </si>
+  <si>
     <t>test+realistic022@example.com</t>
   </si>
   <si>
-    <t>99-1000022</t>
-  </si>
-  <si>
-    <t>Schedule E rental</t>
-  </si>
-  <si>
-    <t>KCON-3023</t>
-  </si>
-  <si>
-    <t>KORG-5023</t>
-  </si>
-  <si>
-    <t>Sarasota Family Trust (TEST)</t>
+    <t>555-0122</t>
+  </si>
+  <si>
+    <t>1022 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Fort Worth</t>
+  </si>
+  <si>
+    <t>76102</t>
+  </si>
+  <si>
+    <t>D3shSTTUVWXY</t>
   </si>
   <si>
     <t>Kai Bell</t>
   </si>
   <si>
+    <t>Kai</t>
+  </si>
+  <si>
+    <t>Bell</t>
+  </si>
+  <si>
+    <t>K. Bell</t>
+  </si>
+  <si>
     <t>test+realistic023@example.com</t>
   </si>
   <si>
-    <t>99-1000023</t>
-  </si>
-  <si>
-    <t>1041; Not Started</t>
-  </si>
-  <si>
-    <t>Estimated tax review</t>
-  </si>
-  <si>
-    <t>KCON-3024</t>
-  </si>
-  <si>
-    <t>KORG-5024</t>
-  </si>
-  <si>
-    <t>Tacoma Arts Alliance (TEST)</t>
+    <t>555-0123</t>
+  </si>
+  <si>
+    <t>1023 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Sarasota</t>
+  </si>
+  <si>
+    <t>34236</t>
+  </si>
+  <si>
+    <t>CzHHx1012345</t>
   </si>
   <si>
     <t>Lane Diaz</t>
   </si>
   <si>
+    <t>Lane</t>
+  </si>
+  <si>
+    <t>Diaz</t>
+  </si>
+  <si>
+    <t>L. Diaz</t>
+  </si>
+  <si>
     <t>test+realistic024@example.com</t>
   </si>
   <si>
-    <t>99-1000024</t>
-  </si>
-  <si>
-    <t>990; In Progress</t>
-  </si>
-  <si>
-    <t>Grant schedule review</t>
+    <t>555-0124</t>
+  </si>
+  <si>
+    <t>1024 Ledger Lane</t>
+  </si>
+  <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>98402</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:O25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -698,917 +878,1142 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L4" t="s">
-        <v>43</v>
+        <v>53</v>
+      </c>
+      <c r="M4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>66</v>
+      </c>
+      <c r="M5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="J6" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="K6" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>77</v>
+      </c>
+      <c r="M6" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="J7" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L7" t="s">
-        <v>72</v>
+        <v>89</v>
+      </c>
+      <c r="M7" t="s">
+        <v>90</v>
+      </c>
+      <c r="N7" t="s">
+        <v>91</v>
+      </c>
+      <c r="O7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s">
-        <v>80</v>
+        <v>100</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="K9" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="L9" t="s">
-        <v>88</v>
+        <v>111</v>
+      </c>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" t="s">
+        <v>112</v>
+      </c>
+      <c r="O9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="J10" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>121</v>
+      </c>
+      <c r="M10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N10" t="s">
+        <v>122</v>
+      </c>
+      <c r="O10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="H11" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="K11" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s">
-        <v>104</v>
+        <v>132</v>
+      </c>
+      <c r="M11" t="s">
+        <v>67</v>
+      </c>
+      <c r="N11" t="s">
+        <v>133</v>
+      </c>
+      <c r="O11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="J12" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s">
-        <v>112</v>
+        <v>142</v>
+      </c>
+      <c r="M12" t="s">
+        <v>78</v>
+      </c>
+      <c r="N12" t="s">
+        <v>143</v>
+      </c>
+      <c r="O12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="H13" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="J13" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="K13" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
+        <v>152</v>
+      </c>
+      <c r="M13" t="s">
+        <v>90</v>
+      </c>
+      <c r="N13" t="s">
+        <v>153</v>
+      </c>
+      <c r="O13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c r="H14" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="K14" t="s">
-        <v>22</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s">
-        <v>127</v>
+        <v>162</v>
+      </c>
+      <c r="M14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" t="s">
+        <v>163</v>
+      </c>
+      <c r="O14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="H15" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="K15" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
+        <v>172</v>
+      </c>
+      <c r="M15" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" t="s">
+        <v>173</v>
+      </c>
+      <c r="O15" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="E16" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="H16" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="J16" t="s">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="K16" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s">
-        <v>143</v>
+        <v>182</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" t="s">
+        <v>183</v>
+      </c>
+      <c r="O16" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="H17" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="J17" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="K17" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s">
-        <v>151</v>
+        <v>192</v>
+      </c>
+      <c r="M17" t="s">
+        <v>67</v>
+      </c>
+      <c r="N17" t="s">
+        <v>193</v>
+      </c>
+      <c r="O17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="H18" t="s">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="J18" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="K18" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s">
-        <v>159</v>
+        <v>202</v>
+      </c>
+      <c r="M18" t="s">
+        <v>78</v>
+      </c>
+      <c r="N18" t="s">
+        <v>203</v>
+      </c>
+      <c r="O18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="H19" t="s">
-        <v>165</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="J19" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="K19" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="L19" t="s">
-        <v>167</v>
+        <v>212</v>
+      </c>
+      <c r="M19" t="s">
+        <v>90</v>
+      </c>
+      <c r="N19" t="s">
+        <v>213</v>
+      </c>
+      <c r="O19" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="H20" t="s">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="J20" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="K20" t="s">
-        <v>22</v>
+        <v>221</v>
       </c>
       <c r="L20" t="s">
-        <v>175</v>
+        <v>222</v>
+      </c>
+      <c r="M20" t="s">
+        <v>223</v>
+      </c>
+      <c r="N20" t="s">
+        <v>224</v>
+      </c>
+      <c r="O20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="D21" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="H21" t="s">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="J21" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
       <c r="K21" t="s">
-        <v>183</v>
+        <v>232</v>
       </c>
       <c r="L21" t="s">
-        <v>184</v>
+        <v>233</v>
+      </c>
+      <c r="M21" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" t="s">
+        <v>234</v>
+      </c>
+      <c r="O21" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="D22" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="E22" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>239</v>
       </c>
       <c r="H22" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="J22" t="s">
-        <v>31</v>
+        <v>241</v>
       </c>
       <c r="K22" t="s">
-        <v>95</v>
+        <v>242</v>
       </c>
       <c r="L22" t="s">
-        <v>191</v>
+        <v>243</v>
+      </c>
+      <c r="M22" t="s">
+        <v>41</v>
+      </c>
+      <c r="N22" t="s">
+        <v>244</v>
+      </c>
+      <c r="O22" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s">
-        <v>193</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="D23" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>249</v>
       </c>
       <c r="H23" t="s">
-        <v>197</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="J23" t="s">
-        <v>41</v>
+        <v>251</v>
       </c>
       <c r="K23" t="s">
-        <v>53</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s">
-        <v>198</v>
+        <v>253</v>
+      </c>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" t="s">
+        <v>254</v>
+      </c>
+      <c r="O23" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="D24" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="E24" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="G24" t="s">
-        <v>18</v>
+        <v>259</v>
       </c>
       <c r="H24" t="s">
-        <v>204</v>
+        <v>49</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>261</v>
       </c>
       <c r="K24" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="L24" t="s">
-        <v>206</v>
+        <v>263</v>
+      </c>
+      <c r="M24" t="s">
+        <v>67</v>
+      </c>
+      <c r="N24" t="s">
+        <v>264</v>
+      </c>
+      <c r="O24" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>207</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="E25" t="s">
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="F25" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>269</v>
       </c>
       <c r="H25" t="s">
-        <v>212</v>
+        <v>62</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="J25" t="s">
-        <v>61</v>
+        <v>271</v>
       </c>
       <c r="K25" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s">
-        <v>214</v>
+        <v>273</v>
+      </c>
+      <c r="M25" t="s">
+        <v>78</v>
+      </c>
+      <c r="N25" t="s">
+        <v>274</v>
+      </c>
+      <c r="O25" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
